--- a/resumo_consolidado_alimentadores_corrigido.xlsx
+++ b/resumo_consolidado_alimentadores_corrigido.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,147 +417,147 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Alimentador</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Cenario</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Convergiu</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Horario_referencia</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>PAC_Inicial</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Metodo_Origem</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Ponta_Eletrica</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Distancia_Ponta_km</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Barras_Totais_Grafo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Barras_Energizadas</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Carregamento_Rede_%</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Fator_Potencia</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Trafo_Alvo_COD_ID</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Trafo_Alvo_kVA</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Carregamento_Trafo_Alvo_%</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Transformadores_Modelados</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Potencia_Carga_Total_kW</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Potencia_Carga_Total_kVA</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Tensao_Minima_pu</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Tensao_Media_pu</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Corrente_Maxima_A</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Perda_Ativa_kW</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Perda_Reativa_kVAr</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Eficiencia_%</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Barras_Abaixo_0_97</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Barras_Abaixo_0_93</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Barras_Abaixo_0_90</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Linhas_Impedancia_Real_BDGD</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Linhas_Impedancia_Estimada</t>
         </is>
@@ -578,7 +566,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NW11</t>
+          <t>NW08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -594,27 +582,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SNW_NW11_9023_BSB006</t>
+          <t>SNW_NW08_11291758</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>automático pela menor DIST (5160)</t>
+          <t>automático por UNI_TR_AT e menor grau</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SNW_NW11_9399_BSB005</t>
+          <t>SNW_NW08_9235_BSB004</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.1180000000000001</v>
+        <v>0.1150000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>508</v>
+        <v>614</v>
       </c>
       <c r="J2" t="n">
-        <v>508</v>
+        <v>614</v>
       </c>
       <c r="K2" t="n">
         <v>60</v>
@@ -624,7 +612,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>FP7288</t>
+          <t>FP8401</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -632,31 +620,31 @@
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="Q2" t="n">
-        <v>3259.56</v>
+        <v>5611.080000000004</v>
       </c>
       <c r="R2" t="n">
-        <v>3543</v>
+        <v>6099</v>
       </c>
       <c r="S2" t="n">
-        <v>0.99842</v>
+        <v>0.99704</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9985555621301775</v>
+        <v>0.9973338825448613</v>
       </c>
       <c r="U2" t="n">
-        <v>145.532</v>
+        <v>260.751</v>
       </c>
       <c r="V2" t="n">
-        <v>31.87242180313968</v>
+        <v>56.81113518652976</v>
       </c>
       <c r="W2" t="n">
-        <v>100.1704823890135</v>
+        <v>173.9045660188924</v>
       </c>
       <c r="X2" t="n">
-        <v>99.02218637475183</v>
+        <v>98.98751870965073</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -671,13 +659,13 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>442</v>
+        <v>516</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NW11</t>
+          <t>NW08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -693,27 +681,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SNW_NW11_9023_BSB006</t>
+          <t>SNW_NW08_11291758</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>automático pela menor DIST (5160)</t>
+          <t>automático por UNI_TR_AT e menor grau</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SNW_NW11_9399_BSB005</t>
+          <t>SNW_NW08_9235_BSB004</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.1180000000000001</v>
+        <v>0.1150000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>508</v>
+        <v>614</v>
       </c>
       <c r="J3" t="n">
-        <v>508</v>
+        <v>614</v>
       </c>
       <c r="K3" t="n">
         <v>80</v>
@@ -723,7 +711,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>FP7288</t>
+          <t>FP8401</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -731,31 +719,31 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="Q3" t="n">
-        <v>4346.080000000001</v>
+        <v>7481.440000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>4724</v>
+        <v>8132</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9978700000000001</v>
+        <v>0.99599</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9980448126232743</v>
+        <v>0.9963903262642742</v>
       </c>
       <c r="U3" t="n">
-        <v>195.441</v>
+        <v>350.326</v>
       </c>
       <c r="V3" t="n">
-        <v>57.48184755506957</v>
+        <v>102.5474500235572</v>
       </c>
       <c r="W3" t="n">
-        <v>180.653396172629</v>
+        <v>313.9006164114425</v>
       </c>
       <c r="X3" t="n">
-        <v>98.67738634458939</v>
+        <v>98.62930866218859</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -770,13 +758,13 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>442</v>
+        <v>516</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NW11</t>
+          <t>NW08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -792,27 +780,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SNW_NW11_9023_BSB006</t>
+          <t>SNW_NW08_11291758</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>automático pela menor DIST (5160)</t>
+          <t>automático por UNI_TR_AT e menor grau</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SNW_NW11_9399_BSB005</t>
+          <t>SNW_NW08_9235_BSB004</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.1180000000000001</v>
+        <v>0.1150000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>508</v>
+        <v>614</v>
       </c>
       <c r="J4" t="n">
-        <v>508</v>
+        <v>614</v>
       </c>
       <c r="K4" t="n">
         <v>100</v>
@@ -822,7 +810,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>FP7288</t>
+          <t>FP8401</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -830,31 +818,31 @@
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="Q4" t="n">
-        <v>5432.599999999999</v>
+        <v>9351.800000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>5905</v>
+        <v>10165</v>
       </c>
       <c r="S4" t="n">
-        <v>0.99729</v>
+        <v>0.99491</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9975184023668637</v>
+        <v>0.9954164600326264</v>
       </c>
       <c r="U4" t="n">
-        <v>246.179</v>
+        <v>441.492</v>
       </c>
       <c r="V4" t="n">
-        <v>91.2002022924553</v>
+        <v>162.8654416707464</v>
       </c>
       <c r="W4" t="n">
-        <v>286.6202967154241</v>
+        <v>498.5279403055411</v>
       </c>
       <c r="X4" t="n">
-        <v>98.32124208864163</v>
+        <v>98.2584588884413</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -869,13 +857,13 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>442</v>
+        <v>516</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NW11</t>
+          <t>NW08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -891,27 +879,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SNW_NW11_9023_BSB006</t>
+          <t>SNW_NW08_11291758</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>automático pela menor DIST (5160)</t>
+          <t>automático por UNI_TR_AT e menor grau</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SNW_NW11_9399_BSB005</t>
+          <t>SNW_NW08_9235_BSB004</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.1180000000000001</v>
+        <v>0.1150000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>508</v>
+        <v>614</v>
       </c>
       <c r="J5" t="n">
-        <v>508</v>
+        <v>614</v>
       </c>
       <c r="K5" t="n">
         <v>120</v>
@@ -921,7 +909,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>FP7288</t>
+          <t>FP8401</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -929,31 +917,31 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="Q5" t="n">
-        <v>6519.120000000001</v>
+        <v>11222.16000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>7086</v>
+        <v>12198</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9967</v>
+        <v>0.9937999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9969757593688363</v>
+        <v>0.994412251223491</v>
       </c>
       <c r="U5" t="n">
-        <v>297.712</v>
+        <v>534.176</v>
       </c>
       <c r="V5" t="n">
-        <v>133.377232467074</v>
+        <v>238.426316610881</v>
       </c>
       <c r="W5" t="n">
-        <v>419.1693933851413</v>
+        <v>729.8113741383956</v>
       </c>
       <c r="X5" t="n">
-        <v>97.95406078631666</v>
+        <v>97.87539727992757</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -968,13 +956,13 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>442</v>
+        <v>516</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NW11</t>
+          <t>NW08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -990,27 +978,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SNW_NW11_9023_BSB006</t>
+          <t>SNW_NW08_11291758</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>automático pela menor DIST (5160)</t>
+          <t>automático por UNI_TR_AT e menor grau</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SNW_NW11_9399_BSB005</t>
+          <t>SNW_NW08_9235_BSB004</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.1180000000000001</v>
+        <v>0.1150000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>508</v>
+        <v>614</v>
       </c>
       <c r="J6" t="n">
-        <v>508</v>
+        <v>614</v>
       </c>
       <c r="K6" t="n">
         <v>160</v>
@@ -1020,7 +1008,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>FP7288</t>
+          <t>FP8401</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1028,31 +1016,31 @@
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="Q6" t="n">
-        <v>8692.160000000002</v>
+        <v>14962.88</v>
       </c>
       <c r="R6" t="n">
-        <v>9448</v>
+        <v>16264</v>
       </c>
       <c r="S6" t="n">
-        <v>0.99554</v>
+        <v>0.99168</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9959064694280079</v>
+        <v>0.9924920228384991</v>
       </c>
       <c r="U6" t="n">
-        <v>397.049</v>
+        <v>708.054</v>
       </c>
       <c r="V6" t="n">
-        <v>237.2587697223483</v>
+        <v>418.8836770202996</v>
       </c>
       <c r="W6" t="n">
-        <v>745.6450994912736</v>
+        <v>1282.234606531772</v>
       </c>
       <c r="X6" t="n">
-        <v>97.27042795205854</v>
+        <v>97.20051435939939</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1067,13 +1055,13 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>442</v>
+        <v>516</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NW11</t>
+          <t>NW08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1089,27 +1077,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SNW_NW11_9023_BSB006</t>
+          <t>SNW_NW08_11291758</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>automático pela menor DIST (5160)</t>
+          <t>automático por UNI_TR_AT e menor grau</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SNW_NW11_9399_BSB005</t>
+          <t>SNW_NW08_9235_BSB004</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.1180000000000001</v>
+        <v>0.1150000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>508</v>
+        <v>614</v>
       </c>
       <c r="J7" t="n">
-        <v>508</v>
+        <v>614</v>
       </c>
       <c r="K7" t="n">
         <v>160</v>
@@ -1119,7 +1107,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>FP7288</t>
+          <t>FP8401</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1127,31 +1115,31 @@
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="Q7" t="n">
-        <v>8030.799999999999</v>
+        <v>13824.4</v>
       </c>
       <c r="R7" t="n">
-        <v>9448</v>
+        <v>16264</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9950899999999999</v>
+        <v>0.99092</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9954503944773175</v>
+        <v>0.9917201957585645</v>
       </c>
       <c r="U7" t="n">
-        <v>393.353</v>
+        <v>701.2140000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>232.862503442782</v>
+        <v>410.8300435809255</v>
       </c>
       <c r="W7" t="n">
-        <v>731.8290227578914</v>
+        <v>1257.581744406474</v>
       </c>
       <c r="X7" t="n">
-        <v>97.10038223535909</v>
+        <v>97.02822514119292</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1166,13 +1154,13 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>442</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NW11</t>
+          <t>NW08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1188,27 +1176,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SNW_NW11_9023_BSB006</t>
+          <t>SNW_NW08_11291758</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>automático pela menor DIST (5160)</t>
+          <t>automático por UNI_TR_AT e menor grau</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SNW_NW11_9399_BSB005</t>
+          <t>SNW_NW08_9235_BSB004</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.1180000000000001</v>
+        <v>0.1150000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>508</v>
+        <v>614</v>
       </c>
       <c r="J8" t="n">
-        <v>508</v>
+        <v>614</v>
       </c>
       <c r="K8" t="n">
         <v>60</v>
@@ -1218,7 +1206,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>FP7288</t>
+          <t>FP8401</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1228,31 +1216,31 @@
         <v>50</v>
       </c>
       <c r="P8" t="n">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="Q8" t="n">
-        <v>3231.96</v>
+        <v>5583.480000000003</v>
       </c>
       <c r="R8" t="n">
-        <v>3513</v>
+        <v>6069</v>
       </c>
       <c r="S8" t="n">
-        <v>0.99844</v>
+        <v>0.9970500000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.998569349112426</v>
+        <v>0.9973462642740619</v>
       </c>
       <c r="U8" t="n">
-        <v>144.228</v>
+        <v>259.444</v>
       </c>
       <c r="V8" t="n">
-        <v>31.36486770164226</v>
+        <v>56.28799559303253</v>
       </c>
       <c r="W8" t="n">
-        <v>98.58713767268989</v>
+        <v>172.3075328816443</v>
       </c>
       <c r="X8" t="n">
-        <v>99.02954035007728</v>
+        <v>98.99188327722079</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1267,13 +1255,13 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>442</v>
+        <v>516</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NW11</t>
+          <t>NW08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1289,27 +1277,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SNW_NW11_9023_BSB006</t>
+          <t>SNW_NW08_11291758</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>automático pela menor DIST (5160)</t>
+          <t>automático por UNI_TR_AT e menor grau</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SNW_NW11_9399_BSB005</t>
+          <t>SNW_NW08_9235_BSB004</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.1180000000000001</v>
+        <v>0.1150000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>508</v>
+        <v>614</v>
       </c>
       <c r="J9" t="n">
-        <v>508</v>
+        <v>614</v>
       </c>
       <c r="K9" t="n">
         <v>60</v>
@@ -1319,7 +1307,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>FP7288</t>
+          <t>FP8401</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1329,31 +1317,31 @@
         <v>80</v>
       </c>
       <c r="P9" t="n">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="Q9" t="n">
-        <v>3314.760000000001</v>
+        <v>5666.280000000003</v>
       </c>
       <c r="R9" t="n">
-        <v>3603</v>
+        <v>6159</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9983999999999998</v>
+        <v>0.99701</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9985300197238659</v>
+        <v>0.9973069004893965</v>
       </c>
       <c r="U9" t="n">
-        <v>148.166</v>
+        <v>263.392</v>
       </c>
       <c r="V9" t="n">
-        <v>33.17448110371537</v>
+        <v>58.14554530888805</v>
       </c>
       <c r="W9" t="n">
-        <v>104.2574007588017</v>
+        <v>178.0209005946481</v>
       </c>
       <c r="X9" t="n">
-        <v>98.99918904826548</v>
+        <v>98.97383212074079</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1368,13 +1356,13 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>442</v>
+        <v>516</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NW11</t>
+          <t>NW08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1390,27 +1378,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SNW_NW11_9023_BSB006</t>
+          <t>SNW_NW08_11291758</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>automático pela menor DIST (5160)</t>
+          <t>automático por UNI_TR_AT e menor grau</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SNW_NW11_9399_BSB005</t>
+          <t>SNW_NW08_9235_BSB004</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.1180000000000001</v>
+        <v>0.1150000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>508</v>
+        <v>614</v>
       </c>
       <c r="J10" t="n">
-        <v>508</v>
+        <v>614</v>
       </c>
       <c r="K10" t="n">
         <v>60</v>
@@ -1420,7 +1408,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>FP7288</t>
+          <t>FP8401</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -1430,31 +1418,31 @@
         <v>100</v>
       </c>
       <c r="P10" t="n">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="Q10" t="n">
-        <v>3369.96</v>
+        <v>5721.480000000003</v>
       </c>
       <c r="R10" t="n">
-        <v>3663</v>
+        <v>6219</v>
       </c>
       <c r="S10" t="n">
-        <v>0.99837</v>
+        <v>0.9969800000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.99850191321499</v>
+        <v>0.9972791517128875</v>
       </c>
       <c r="U10" t="n">
-        <v>150.85</v>
+        <v>266.092</v>
       </c>
       <c r="V10" t="n">
-        <v>34.87955317447825</v>
+        <v>59.88890068774531</v>
       </c>
       <c r="W10" t="n">
-        <v>109.634380706403</v>
+        <v>183.4448829930051</v>
       </c>
       <c r="X10" t="n">
-        <v>98.96498613709129</v>
+        <v>98.95326208100448</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1469,13 +1457,13 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>442</v>
+        <v>516</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NW11</t>
+          <t>NW08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1491,27 +1479,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SNW_NW11_9023_BSB006</t>
+          <t>SNW_NW08_11291758</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>automático pela menor DIST (5160)</t>
+          <t>automático por UNI_TR_AT e menor grau</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SNW_NW11_9399_BSB005</t>
+          <t>SNW_NW08_9235_BSB004</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.1180000000000001</v>
+        <v>0.1150000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>508</v>
+        <v>614</v>
       </c>
       <c r="J11" t="n">
-        <v>508</v>
+        <v>614</v>
       </c>
       <c r="K11" t="n">
         <v>60</v>
@@ -1521,7 +1509,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>FP7288</t>
+          <t>FP8401</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1531,31 +1519,31 @@
         <v>120</v>
       </c>
       <c r="P11" t="n">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="Q11" t="n">
-        <v>3425.16</v>
+        <v>5776.680000000004</v>
       </c>
       <c r="R11" t="n">
-        <v>3723</v>
+        <v>6279</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9983400000000001</v>
+        <v>0.99695</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9984736291913215</v>
+        <v>0.9972514845024469</v>
       </c>
       <c r="U11" t="n">
-        <v>153.562</v>
+        <v>268.811</v>
       </c>
       <c r="V11" t="n">
-        <v>36.99539896968672</v>
+        <v>62.0407133676758</v>
       </c>
       <c r="W11" t="n">
-        <v>116.3279354949319</v>
+        <v>190.175689816466</v>
       </c>
       <c r="X11" t="n">
-        <v>98.91989282341009</v>
+        <v>98.92601436521193</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1570,13 +1558,13 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>442</v>
+        <v>516</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NW11</t>
+          <t>NW08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1592,27 +1580,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SNW_NW11_9023_BSB006</t>
+          <t>SNW_NW08_11291758</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>automático pela menor DIST (5160)</t>
+          <t>automático por UNI_TR_AT e menor grau</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SNW_NW11_9399_BSB005</t>
+          <t>SNW_NW08_9235_BSB004</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.1180000000000001</v>
+        <v>0.1150000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>508</v>
+        <v>614</v>
       </c>
       <c r="J12" t="n">
-        <v>508</v>
+        <v>614</v>
       </c>
       <c r="K12" t="n">
         <v>60</v>
@@ -1622,7 +1610,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>FP7288</t>
+          <t>FP8401</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -1632,31 +1620,31 @@
         <v>150</v>
       </c>
       <c r="P12" t="n">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="Q12" t="n">
-        <v>3507.96</v>
+        <v>5859.480000000003</v>
       </c>
       <c r="R12" t="n">
-        <v>3813</v>
+        <v>6369</v>
       </c>
       <c r="S12" t="n">
-        <v>0.99829</v>
+        <v>0.9969100000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9984312820512823</v>
+        <v>0.997209021207178</v>
       </c>
       <c r="U12" t="n">
-        <v>157.648</v>
+        <v>272.86</v>
       </c>
       <c r="V12" t="n">
-        <v>40.92842932317104</v>
+        <v>65.97847962436911</v>
       </c>
       <c r="W12" t="n">
-        <v>128.801646591237</v>
+        <v>202.5520561858301</v>
       </c>
       <c r="X12" t="n">
-        <v>98.83326978291738</v>
+        <v>98.87398745922216</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -1671,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>442</v>
+        <v>516</v>
       </c>
     </row>
   </sheetData>
